--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120330298</v>
+        <v>120330293</v>
       </c>
       <c r="B2" t="n">
-        <v>77474</v>
+        <v>78279</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380418</v>
+        <v>380661</v>
       </c>
       <c r="R2" t="n">
-        <v>6729265</v>
+        <v>6729256</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330323</v>
+        <v>120330317</v>
       </c>
       <c r="B3" t="n">
-        <v>78576</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380832</v>
+        <v>380654</v>
       </c>
       <c r="R3" t="n">
-        <v>6728895</v>
+        <v>6728875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330317</v>
+        <v>120330289</v>
       </c>
       <c r="B4" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380654</v>
+        <v>380729</v>
       </c>
       <c r="R4" t="n">
-        <v>6728875</v>
+        <v>6729223</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330296</v>
+        <v>120330315</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380544</v>
+        <v>380671</v>
       </c>
       <c r="R5" t="n">
-        <v>6729316</v>
+        <v>6728902</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330295</v>
+        <v>120330322</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380564</v>
+        <v>380814</v>
       </c>
       <c r="R6" t="n">
-        <v>6729347</v>
+        <v>6728859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330292</v>
+        <v>120330310</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380661</v>
+        <v>380648</v>
       </c>
       <c r="R7" t="n">
-        <v>6729256</v>
+        <v>6729011</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330289</v>
+        <v>120330324</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380729</v>
+        <v>380873</v>
       </c>
       <c r="R8" t="n">
-        <v>6729223</v>
+        <v>6728919</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330320</v>
+        <v>120330304</v>
       </c>
       <c r="B9" t="n">
-        <v>74646</v>
+        <v>80499</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>1049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380766</v>
+        <v>380372</v>
       </c>
       <c r="R9" t="n">
-        <v>6728820</v>
+        <v>6729180</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120330321</v>
+        <v>120330316</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380786</v>
+        <v>380649</v>
       </c>
       <c r="R10" t="n">
-        <v>6728836</v>
+        <v>6728874</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120330304</v>
+        <v>120330294</v>
       </c>
       <c r="B11" t="n">
-        <v>80499</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380372</v>
+        <v>380570</v>
       </c>
       <c r="R11" t="n">
-        <v>6729180</v>
+        <v>6729359</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330305</v>
+        <v>120330296</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380455</v>
+        <v>380544</v>
       </c>
       <c r="R12" t="n">
-        <v>6729080</v>
+        <v>6729316</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120330309</v>
+        <v>120330306</v>
       </c>
       <c r="B13" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380597</v>
+        <v>380509</v>
       </c>
       <c r="R13" t="n">
-        <v>6728960</v>
+        <v>6729054</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330293</v>
+        <v>120330297</v>
       </c>
       <c r="B14" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380661</v>
+        <v>380445</v>
       </c>
       <c r="R14" t="n">
-        <v>6729256</v>
+        <v>6729259</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120330287</v>
+        <v>120330291</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380785</v>
+        <v>380708</v>
       </c>
       <c r="R15" t="n">
-        <v>6729186</v>
+        <v>6729212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120330322</v>
+        <v>120330309</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380814</v>
+        <v>380597</v>
       </c>
       <c r="R16" t="n">
-        <v>6728859</v>
+        <v>6728960</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120330311</v>
+        <v>120330302</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380640</v>
+        <v>380378</v>
       </c>
       <c r="R17" t="n">
-        <v>6729019</v>
+        <v>6729224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2289,6 +2289,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2307,10 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120330303</v>
+        <v>120330301</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2323,21 +2324,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2347,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380366</v>
+        <v>380391</v>
       </c>
       <c r="R18" t="n">
-        <v>6729220</v>
+        <v>6729218</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2391,6 +2392,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2409,10 +2411,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330318</v>
+        <v>120330299</v>
       </c>
       <c r="B19" t="n">
-        <v>56784</v>
+        <v>78278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2427,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102961</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380696</v>
+        <v>380431</v>
       </c>
       <c r="R19" t="n">
-        <v>6728743</v>
+        <v>6729232</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2513,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330286</v>
+        <v>120330321</v>
       </c>
       <c r="B20" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380781</v>
+        <v>380786</v>
       </c>
       <c r="R20" t="n">
-        <v>6729159</v>
+        <v>6728836</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330302</v>
+        <v>120330286</v>
       </c>
       <c r="B21" t="n">
-        <v>79160</v>
+        <v>86895</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2631,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>510</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380378</v>
+        <v>380781</v>
       </c>
       <c r="R21" t="n">
-        <v>6729224</v>
+        <v>6729159</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,7 +2699,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2716,7 +2717,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330288</v>
+        <v>120330290</v>
       </c>
       <c r="B22" t="n">
         <v>78576</v>
@@ -2756,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380750</v>
+        <v>380721</v>
       </c>
       <c r="R22" t="n">
-        <v>6729215</v>
+        <v>6729221</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330310</v>
+        <v>120330313</v>
       </c>
       <c r="B23" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2830,25 +2831,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2858,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380648</v>
+        <v>380704</v>
       </c>
       <c r="R23" t="n">
-        <v>6729011</v>
+        <v>6729068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,10 +2921,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120330294</v>
+        <v>120330319</v>
       </c>
       <c r="B24" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2932,25 +2933,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380570</v>
+        <v>380743</v>
       </c>
       <c r="R24" t="n">
-        <v>6729359</v>
+        <v>6728768</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120330324</v>
+        <v>120330285</v>
       </c>
       <c r="B25" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380873</v>
+        <v>380783</v>
       </c>
       <c r="R25" t="n">
-        <v>6728919</v>
+        <v>6729158</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,7 +3125,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120330315</v>
+        <v>120330312</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3164,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380671</v>
+        <v>380707</v>
       </c>
       <c r="R26" t="n">
-        <v>6728902</v>
+        <v>6729068</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3226,10 +3227,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120330306</v>
+        <v>120330300</v>
       </c>
       <c r="B27" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,21 +3243,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3267,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380509</v>
+        <v>380431</v>
       </c>
       <c r="R27" t="n">
-        <v>6729054</v>
+        <v>6729232</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3328,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120330308</v>
+        <v>120330298</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>77474</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3368,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380515</v>
+        <v>380418</v>
       </c>
       <c r="R28" t="n">
-        <v>6729057</v>
+        <v>6729265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,10 +3431,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120330300</v>
+        <v>120330320</v>
       </c>
       <c r="B29" t="n">
-        <v>78279</v>
+        <v>74646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,21 +3447,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3471,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380431</v>
+        <v>380766</v>
       </c>
       <c r="R29" t="n">
-        <v>6729232</v>
+        <v>6728820</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3532,10 +3533,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120330301</v>
+        <v>120330323</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,21 +3549,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3572,10 +3573,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380391</v>
+        <v>380832</v>
       </c>
       <c r="R30" t="n">
-        <v>6729218</v>
+        <v>6728895</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,7 +3617,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330299</v>
+        <v>120330318</v>
       </c>
       <c r="B31" t="n">
-        <v>78278</v>
+        <v>56784</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>102961</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380431</v>
+        <v>380696</v>
       </c>
       <c r="R31" t="n">
-        <v>6729232</v>
+        <v>6728743</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330312</v>
+        <v>120330292</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380707</v>
+        <v>380661</v>
       </c>
       <c r="R32" t="n">
-        <v>6729068</v>
+        <v>6729256</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330290</v>
+        <v>120330287</v>
       </c>
       <c r="B33" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3855,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380721</v>
+        <v>380785</v>
       </c>
       <c r="R33" t="n">
-        <v>6729221</v>
+        <v>6729186</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330316</v>
+        <v>120330311</v>
       </c>
       <c r="B34" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3953,25 +3953,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380649</v>
+        <v>380640</v>
       </c>
       <c r="R34" t="n">
-        <v>6728874</v>
+        <v>6729019</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330319</v>
+        <v>120330308</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4055,25 +4055,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380743</v>
+        <v>380515</v>
       </c>
       <c r="R35" t="n">
-        <v>6728768</v>
+        <v>6729057</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330297</v>
+        <v>120330288</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380445</v>
+        <v>380750</v>
       </c>
       <c r="R36" t="n">
-        <v>6729259</v>
+        <v>6729215</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330291</v>
+        <v>120330303</v>
       </c>
       <c r="B37" t="n">
         <v>78542</v>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380708</v>
+        <v>380366</v>
       </c>
       <c r="R37" t="n">
-        <v>6729212</v>
+        <v>6729220</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120330285</v>
+        <v>120330305</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380783</v>
+        <v>380455</v>
       </c>
       <c r="R38" t="n">
-        <v>6729158</v>
+        <v>6729080</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120330313</v>
+        <v>120330295</v>
       </c>
       <c r="B39" t="n">
         <v>78542</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380704</v>
+        <v>380564</v>
       </c>
       <c r="R39" t="n">
-        <v>6729068</v>
+        <v>6729347</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330310</v>
+        <v>120330324</v>
       </c>
       <c r="B7" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380648</v>
+        <v>380873</v>
       </c>
       <c r="R7" t="n">
-        <v>6729011</v>
+        <v>6728919</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330324</v>
+        <v>120330310</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380873</v>
+        <v>380648</v>
       </c>
       <c r="R8" t="n">
-        <v>6728919</v>
+        <v>6729011</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -2411,10 +2411,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330299</v>
+        <v>120330286</v>
       </c>
       <c r="B19" t="n">
-        <v>78278</v>
+        <v>86895</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2427,21 +2427,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380431</v>
+        <v>380781</v>
       </c>
       <c r="R19" t="n">
-        <v>6729232</v>
+        <v>6729159</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,10 +2513,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330321</v>
+        <v>120330299</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2529,21 +2529,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380786</v>
+        <v>380431</v>
       </c>
       <c r="R20" t="n">
-        <v>6728836</v>
+        <v>6729232</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330286</v>
+        <v>120330321</v>
       </c>
       <c r="B21" t="n">
-        <v>86895</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2631,21 +2631,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380781</v>
+        <v>380786</v>
       </c>
       <c r="R21" t="n">
-        <v>6729159</v>
+        <v>6728836</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,10 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330290</v>
+        <v>120330313</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2733,21 +2733,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380721</v>
+        <v>380704</v>
       </c>
       <c r="R22" t="n">
-        <v>6729221</v>
+        <v>6729068</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330313</v>
+        <v>120330290</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2835,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380704</v>
+        <v>380721</v>
       </c>
       <c r="R23" t="n">
-        <v>6729068</v>
+        <v>6729221</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330292</v>
+        <v>120330287</v>
       </c>
       <c r="B32" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380661</v>
+        <v>380785</v>
       </c>
       <c r="R32" t="n">
-        <v>6729256</v>
+        <v>6729186</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3839,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330287</v>
+        <v>120330311</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380785</v>
+        <v>380640</v>
       </c>
       <c r="R33" t="n">
-        <v>6729186</v>
+        <v>6729019</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330311</v>
+        <v>120330292</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380640</v>
+        <v>380661</v>
       </c>
       <c r="R34" t="n">
-        <v>6729019</v>
+        <v>6729256</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120330293</v>
+        <v>120330298</v>
       </c>
       <c r="B2" t="n">
-        <v>78279</v>
+        <v>77474</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380661</v>
+        <v>380418</v>
       </c>
       <c r="R2" t="n">
-        <v>6729256</v>
+        <v>6729265</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330317</v>
+        <v>120330292</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>78278</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380654</v>
+        <v>380661</v>
       </c>
       <c r="R3" t="n">
-        <v>6728875</v>
+        <v>6729256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330289</v>
+        <v>120330313</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380729</v>
+        <v>380704</v>
       </c>
       <c r="R4" t="n">
-        <v>6729223</v>
+        <v>6729068</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330315</v>
+        <v>120330303</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380671</v>
+        <v>380366</v>
       </c>
       <c r="R5" t="n">
-        <v>6728902</v>
+        <v>6729220</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330322</v>
+        <v>120330301</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380814</v>
+        <v>380391</v>
       </c>
       <c r="R6" t="n">
-        <v>6728859</v>
+        <v>6729218</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,6 +1167,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330324</v>
+        <v>120330288</v>
       </c>
       <c r="B7" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380873</v>
+        <v>380750</v>
       </c>
       <c r="R7" t="n">
-        <v>6728919</v>
+        <v>6729215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330310</v>
+        <v>120330324</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380648</v>
+        <v>380873</v>
       </c>
       <c r="R8" t="n">
-        <v>6729011</v>
+        <v>6728919</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330304</v>
+        <v>120330297</v>
       </c>
       <c r="B9" t="n">
-        <v>80499</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1406,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380372</v>
+        <v>380445</v>
       </c>
       <c r="R9" t="n">
-        <v>6729180</v>
+        <v>6729259</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120330316</v>
+        <v>120330287</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1504,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380649</v>
+        <v>380785</v>
       </c>
       <c r="R10" t="n">
-        <v>6728874</v>
+        <v>6729186</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120330294</v>
+        <v>120330293</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380570</v>
+        <v>380661</v>
       </c>
       <c r="R11" t="n">
-        <v>6729359</v>
+        <v>6729256</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330296</v>
+        <v>120330317</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380544</v>
+        <v>380654</v>
       </c>
       <c r="R12" t="n">
-        <v>6729316</v>
+        <v>6728875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120330306</v>
+        <v>120330305</v>
       </c>
       <c r="B13" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1814,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380509</v>
+        <v>380455</v>
       </c>
       <c r="R13" t="n">
-        <v>6729054</v>
+        <v>6729080</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330297</v>
+        <v>120330300</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1916,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380445</v>
+        <v>380431</v>
       </c>
       <c r="R14" t="n">
-        <v>6729259</v>
+        <v>6729232</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2002,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120330291</v>
+        <v>120330322</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2041,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380708</v>
+        <v>380814</v>
       </c>
       <c r="R15" t="n">
-        <v>6729212</v>
+        <v>6728859</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120330309</v>
+        <v>120330295</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2116,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380597</v>
+        <v>380564</v>
       </c>
       <c r="R16" t="n">
-        <v>6728960</v>
+        <v>6729347</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120330302</v>
+        <v>120330310</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>90545</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2217,25 +2218,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380378</v>
+        <v>380648</v>
       </c>
       <c r="R17" t="n">
-        <v>6729224</v>
+        <v>6729011</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2289,7 +2290,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2308,10 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120330301</v>
+        <v>120330311</v>
       </c>
       <c r="B18" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,21 +2324,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380391</v>
+        <v>380640</v>
       </c>
       <c r="R18" t="n">
-        <v>6729218</v>
+        <v>6729019</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2392,7 +2392,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2411,10 +2410,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330286</v>
+        <v>120330316</v>
       </c>
       <c r="B19" t="n">
-        <v>86895</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2423,25 +2422,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2451,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380781</v>
+        <v>380649</v>
       </c>
       <c r="R19" t="n">
-        <v>6729159</v>
+        <v>6728874</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2513,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330299</v>
+        <v>120330294</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2529,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380431</v>
+        <v>380570</v>
       </c>
       <c r="R20" t="n">
-        <v>6729232</v>
+        <v>6729359</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330321</v>
+        <v>120330306</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2631,21 +2630,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380786</v>
+        <v>380509</v>
       </c>
       <c r="R21" t="n">
-        <v>6728836</v>
+        <v>6729054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,10 +2716,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330313</v>
+        <v>120330286</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2733,21 +2732,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380704</v>
+        <v>380781</v>
       </c>
       <c r="R22" t="n">
-        <v>6729068</v>
+        <v>6729159</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,7 +2818,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330290</v>
+        <v>120330323</v>
       </c>
       <c r="B23" t="n">
         <v>78576</v>
@@ -2859,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380721</v>
+        <v>380832</v>
       </c>
       <c r="R23" t="n">
-        <v>6729221</v>
+        <v>6728895</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,10 +2920,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120330319</v>
+        <v>120330285</v>
       </c>
       <c r="B24" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2933,25 +2932,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2961,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380743</v>
+        <v>380783</v>
       </c>
       <c r="R24" t="n">
-        <v>6728768</v>
+        <v>6729158</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,7 +3022,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120330285</v>
+        <v>120330315</v>
       </c>
       <c r="B25" t="n">
         <v>78542</v>
@@ -3063,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380783</v>
+        <v>380671</v>
       </c>
       <c r="R25" t="n">
-        <v>6729158</v>
+        <v>6728902</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,10 +3124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120330312</v>
+        <v>120330299</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3141,21 +3140,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3165,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380707</v>
+        <v>380431</v>
       </c>
       <c r="R26" t="n">
-        <v>6729068</v>
+        <v>6729232</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120330300</v>
+        <v>120330302</v>
       </c>
       <c r="B27" t="n">
-        <v>78279</v>
+        <v>79160</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3243,21 +3242,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3267,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380431</v>
+        <v>380378</v>
       </c>
       <c r="R27" t="n">
-        <v>6729232</v>
+        <v>6729224</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,6 +3310,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120330298</v>
+        <v>120330321</v>
       </c>
       <c r="B28" t="n">
-        <v>77474</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380418</v>
+        <v>380786</v>
       </c>
       <c r="R28" t="n">
-        <v>6729265</v>
+        <v>6728836</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120330320</v>
+        <v>120330296</v>
       </c>
       <c r="B29" t="n">
-        <v>74646</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3447,21 +3447,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380766</v>
+        <v>380544</v>
       </c>
       <c r="R29" t="n">
-        <v>6728820</v>
+        <v>6729316</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120330323</v>
+        <v>120330312</v>
       </c>
       <c r="B30" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380832</v>
+        <v>380707</v>
       </c>
       <c r="R30" t="n">
-        <v>6728895</v>
+        <v>6729068</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330318</v>
+        <v>120330309</v>
       </c>
       <c r="B31" t="n">
-        <v>56784</v>
+        <v>90545</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3647,25 +3647,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102961</v>
+        <v>5447</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380696</v>
+        <v>380597</v>
       </c>
       <c r="R31" t="n">
-        <v>6728743</v>
+        <v>6728960</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330287</v>
+        <v>120330290</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380785</v>
+        <v>380721</v>
       </c>
       <c r="R32" t="n">
-        <v>6729186</v>
+        <v>6729221</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,7 +3839,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330311</v>
+        <v>120330289</v>
       </c>
       <c r="B33" t="n">
         <v>78542</v>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380640</v>
+        <v>380729</v>
       </c>
       <c r="R33" t="n">
-        <v>6729019</v>
+        <v>6729223</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330292</v>
+        <v>120330291</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3957,21 +3957,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380661</v>
+        <v>380708</v>
       </c>
       <c r="R34" t="n">
-        <v>6729256</v>
+        <v>6729212</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330308</v>
+        <v>120330320</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4059,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380515</v>
+        <v>380766</v>
       </c>
       <c r="R35" t="n">
-        <v>6729057</v>
+        <v>6728820</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330288</v>
+        <v>120330308</v>
       </c>
       <c r="B36" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380750</v>
+        <v>380515</v>
       </c>
       <c r="R36" t="n">
-        <v>6729215</v>
+        <v>6729057</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330303</v>
+        <v>120330319</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4259,25 +4259,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380366</v>
+        <v>380743</v>
       </c>
       <c r="R37" t="n">
-        <v>6729220</v>
+        <v>6728768</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120330305</v>
+        <v>120330304</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>80499</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380455</v>
+        <v>380372</v>
       </c>
       <c r="R38" t="n">
-        <v>6729080</v>
+        <v>6729180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120330295</v>
+        <v>120330318</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>56784</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>102961</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380564</v>
+        <v>380696</v>
       </c>
       <c r="R39" t="n">
-        <v>6729347</v>
+        <v>6728743</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330309</v>
+        <v>120330290</v>
       </c>
       <c r="B31" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3647,25 +3647,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380597</v>
+        <v>380721</v>
       </c>
       <c r="R31" t="n">
-        <v>6728960</v>
+        <v>6729221</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330290</v>
+        <v>120330289</v>
       </c>
       <c r="B32" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3753,21 +3753,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380721</v>
+        <v>380729</v>
       </c>
       <c r="R32" t="n">
-        <v>6729221</v>
+        <v>6729223</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330289</v>
+        <v>120330309</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3851,25 +3851,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380729</v>
+        <v>380597</v>
       </c>
       <c r="R33" t="n">
-        <v>6729223</v>
+        <v>6728960</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330320</v>
+        <v>120330319</v>
       </c>
       <c r="B35" t="n">
-        <v>74646</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4055,25 +4055,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380766</v>
+        <v>380743</v>
       </c>
       <c r="R35" t="n">
-        <v>6728820</v>
+        <v>6728768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330308</v>
+        <v>120330320</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380515</v>
+        <v>380766</v>
       </c>
       <c r="R36" t="n">
-        <v>6729057</v>
+        <v>6728820</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330319</v>
+        <v>120330308</v>
       </c>
       <c r="B37" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4259,25 +4259,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380743</v>
+        <v>380515</v>
       </c>
       <c r="R37" t="n">
-        <v>6728768</v>
+        <v>6729057</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330292</v>
+        <v>120330321</v>
       </c>
       <c r="B3" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380661</v>
+        <v>380786</v>
       </c>
       <c r="R3" t="n">
-        <v>6729256</v>
+        <v>6728836</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330313</v>
+        <v>120330288</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380704</v>
+        <v>380750</v>
       </c>
       <c r="R4" t="n">
-        <v>6729068</v>
+        <v>6729215</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330303</v>
+        <v>120330304</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>80499</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380366</v>
+        <v>380372</v>
       </c>
       <c r="R5" t="n">
-        <v>6729220</v>
+        <v>6729180</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330301</v>
+        <v>120330322</v>
       </c>
       <c r="B6" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380391</v>
+        <v>380814</v>
       </c>
       <c r="R6" t="n">
-        <v>6729218</v>
+        <v>6728859</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1167,7 +1167,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1186,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330288</v>
+        <v>120330295</v>
       </c>
       <c r="B7" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380750</v>
+        <v>380564</v>
       </c>
       <c r="R7" t="n">
-        <v>6729215</v>
+        <v>6729347</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330324</v>
+        <v>120330310</v>
       </c>
       <c r="B8" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1300,25 +1299,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1328,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380873</v>
+        <v>380648</v>
       </c>
       <c r="R8" t="n">
-        <v>6728919</v>
+        <v>6729011</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330297</v>
+        <v>120330319</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1402,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380445</v>
+        <v>380743</v>
       </c>
       <c r="R9" t="n">
-        <v>6729259</v>
+        <v>6728768</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120330287</v>
+        <v>120330317</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380785</v>
+        <v>380654</v>
       </c>
       <c r="R10" t="n">
-        <v>6729186</v>
+        <v>6728875</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120330293</v>
+        <v>120330318</v>
       </c>
       <c r="B11" t="n">
-        <v>78279</v>
+        <v>56784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>102961</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380661</v>
+        <v>380696</v>
       </c>
       <c r="R11" t="n">
-        <v>6729256</v>
+        <v>6728743</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330317</v>
+        <v>120330290</v>
       </c>
       <c r="B12" t="n">
-        <v>82321</v>
+        <v>78576</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1736,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380654</v>
+        <v>380721</v>
       </c>
       <c r="R12" t="n">
-        <v>6728875</v>
+        <v>6729221</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120330305</v>
+        <v>120330301</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380455</v>
+        <v>380391</v>
       </c>
       <c r="R13" t="n">
-        <v>6729080</v>
+        <v>6729218</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,6 +1881,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330300</v>
+        <v>120330294</v>
       </c>
       <c r="B14" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,21 +1916,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380431</v>
+        <v>380570</v>
       </c>
       <c r="R14" t="n">
-        <v>6729232</v>
+        <v>6729359</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120330322</v>
+        <v>120330299</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,21 +2018,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380814</v>
+        <v>380431</v>
       </c>
       <c r="R15" t="n">
-        <v>6728859</v>
+        <v>6729232</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120330295</v>
+        <v>120330324</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380564</v>
+        <v>380873</v>
       </c>
       <c r="R16" t="n">
-        <v>6729347</v>
+        <v>6728919</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120330310</v>
+        <v>120330302</v>
       </c>
       <c r="B17" t="n">
-        <v>90545</v>
+        <v>79160</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2218,25 +2218,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380648</v>
+        <v>380378</v>
       </c>
       <c r="R17" t="n">
-        <v>6729011</v>
+        <v>6729224</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,6 +2290,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2308,7 +2309,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120330311</v>
+        <v>120330297</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2348,10 +2349,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380640</v>
+        <v>380445</v>
       </c>
       <c r="R18" t="n">
-        <v>6729019</v>
+        <v>6729259</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,10 +2411,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330316</v>
+        <v>120330305</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2422,25 +2423,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380649</v>
+        <v>380455</v>
       </c>
       <c r="R19" t="n">
-        <v>6728874</v>
+        <v>6729080</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,7 +2513,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330294</v>
+        <v>120330296</v>
       </c>
       <c r="B20" t="n">
         <v>78542</v>
@@ -2552,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380570</v>
+        <v>380544</v>
       </c>
       <c r="R20" t="n">
-        <v>6729359</v>
+        <v>6729316</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,10 +2615,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330306</v>
+        <v>120330316</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2626,25 +2627,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2654,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380509</v>
+        <v>380649</v>
       </c>
       <c r="R21" t="n">
-        <v>6729054</v>
+        <v>6728874</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,10 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330286</v>
+        <v>120330323</v>
       </c>
       <c r="B22" t="n">
-        <v>86895</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,21 +2733,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380781</v>
+        <v>380832</v>
       </c>
       <c r="R22" t="n">
-        <v>6729159</v>
+        <v>6728895</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330323</v>
+        <v>120330311</v>
       </c>
       <c r="B23" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2858,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380832</v>
+        <v>380640</v>
       </c>
       <c r="R23" t="n">
-        <v>6728895</v>
+        <v>6729019</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,7 +2921,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120330285</v>
+        <v>120330287</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -2960,10 +2961,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380783</v>
+        <v>380785</v>
       </c>
       <c r="R24" t="n">
-        <v>6729158</v>
+        <v>6729186</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120330315</v>
+        <v>120330286</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380671</v>
+        <v>380781</v>
       </c>
       <c r="R25" t="n">
-        <v>6728902</v>
+        <v>6729159</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,10 +3125,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120330299</v>
+        <v>120330312</v>
       </c>
       <c r="B26" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,21 +3141,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3164,10 +3165,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380431</v>
+        <v>380707</v>
       </c>
       <c r="R26" t="n">
-        <v>6729232</v>
+        <v>6729068</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3226,10 +3227,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120330302</v>
+        <v>120330291</v>
       </c>
       <c r="B27" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,21 +3243,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3267,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380378</v>
+        <v>380708</v>
       </c>
       <c r="R27" t="n">
-        <v>6729224</v>
+        <v>6729212</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3310,7 +3311,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3329,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120330321</v>
+        <v>120330320</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>74646</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3345,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380786</v>
+        <v>380766</v>
       </c>
       <c r="R28" t="n">
-        <v>6728836</v>
+        <v>6728820</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,10 +3431,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120330296</v>
+        <v>120330300</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3447,21 +3447,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3471,10 +3471,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380544</v>
+        <v>380431</v>
       </c>
       <c r="R29" t="n">
-        <v>6729316</v>
+        <v>6729232</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120330312</v>
+        <v>120330315</v>
       </c>
       <c r="B30" t="n">
         <v>78542</v>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380707</v>
+        <v>380671</v>
       </c>
       <c r="R30" t="n">
-        <v>6729068</v>
+        <v>6728902</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330290</v>
+        <v>120330285</v>
       </c>
       <c r="B31" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380721</v>
+        <v>380783</v>
       </c>
       <c r="R31" t="n">
-        <v>6729221</v>
+        <v>6729158</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,7 +3737,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330289</v>
+        <v>120330303</v>
       </c>
       <c r="B32" t="n">
         <v>78542</v>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380729</v>
+        <v>380366</v>
       </c>
       <c r="R32" t="n">
-        <v>6729223</v>
+        <v>6729220</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330309</v>
+        <v>120330292</v>
       </c>
       <c r="B33" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3851,25 +3851,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380597</v>
+        <v>380661</v>
       </c>
       <c r="R33" t="n">
-        <v>6728960</v>
+        <v>6729256</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,7 +3941,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330291</v>
+        <v>120330289</v>
       </c>
       <c r="B34" t="n">
         <v>78542</v>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380708</v>
+        <v>380729</v>
       </c>
       <c r="R34" t="n">
-        <v>6729212</v>
+        <v>6729223</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330319</v>
+        <v>120330308</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4055,25 +4055,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380743</v>
+        <v>380515</v>
       </c>
       <c r="R35" t="n">
-        <v>6728768</v>
+        <v>6729057</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330320</v>
+        <v>120330313</v>
       </c>
       <c r="B36" t="n">
-        <v>74646</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380766</v>
+        <v>380704</v>
       </c>
       <c r="R36" t="n">
-        <v>6728820</v>
+        <v>6729068</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330308</v>
+        <v>120330306</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380515</v>
+        <v>380509</v>
       </c>
       <c r="R37" t="n">
-        <v>6729057</v>
+        <v>6729054</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120330304</v>
+        <v>120330309</v>
       </c>
       <c r="B38" t="n">
-        <v>80499</v>
+        <v>90545</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4361,25 +4361,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1049</v>
+        <v>5447</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380372</v>
+        <v>380597</v>
       </c>
       <c r="R38" t="n">
-        <v>6729180</v>
+        <v>6728960</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120330318</v>
+        <v>120330293</v>
       </c>
       <c r="B39" t="n">
-        <v>56784</v>
+        <v>78279</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102961</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380696</v>
+        <v>380661</v>
       </c>
       <c r="R39" t="n">
-        <v>6728743</v>
+        <v>6729256</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330290</v>
+        <v>120330294</v>
       </c>
       <c r="B12" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380721</v>
+        <v>380570</v>
       </c>
       <c r="R12" t="n">
-        <v>6729221</v>
+        <v>6729359</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330294</v>
+        <v>120330290</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,21 +1916,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380570</v>
+        <v>380721</v>
       </c>
       <c r="R14" t="n">
-        <v>6729359</v>
+        <v>6729221</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120330298</v>
+        <v>120330303</v>
       </c>
       <c r="B2" t="n">
-        <v>77474</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380418</v>
+        <v>380366</v>
       </c>
       <c r="R2" t="n">
-        <v>6729265</v>
+        <v>6729220</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330321</v>
+        <v>120330317</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380786</v>
+        <v>380654</v>
       </c>
       <c r="R3" t="n">
-        <v>6728836</v>
+        <v>6728875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330288</v>
+        <v>120330301</v>
       </c>
       <c r="B4" t="n">
-        <v>78576</v>
+        <v>78278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380750</v>
+        <v>380391</v>
       </c>
       <c r="R4" t="n">
-        <v>6729215</v>
+        <v>6729218</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -981,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330304</v>
+        <v>120330289</v>
       </c>
       <c r="B5" t="n">
-        <v>80499</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1022,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380372</v>
+        <v>380729</v>
       </c>
       <c r="R5" t="n">
-        <v>6729180</v>
+        <v>6729223</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1084,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330322</v>
+        <v>120330293</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1100,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1124,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380814</v>
+        <v>380661</v>
       </c>
       <c r="R6" t="n">
-        <v>6728859</v>
+        <v>6729256</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1186,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330295</v>
+        <v>120330304</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>80499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1202,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1226,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380564</v>
+        <v>380372</v>
       </c>
       <c r="R7" t="n">
-        <v>6729347</v>
+        <v>6729180</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1288,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330310</v>
+        <v>120330313</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1299,25 +1300,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1328,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380648</v>
+        <v>380704</v>
       </c>
       <c r="R8" t="n">
-        <v>6729011</v>
+        <v>6729068</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1390,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330319</v>
+        <v>120330298</v>
       </c>
       <c r="B9" t="n">
-        <v>90545</v>
+        <v>77474</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1402,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380743</v>
+        <v>380418</v>
       </c>
       <c r="R9" t="n">
-        <v>6728768</v>
+        <v>6729265</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120330317</v>
+        <v>120330291</v>
       </c>
       <c r="B10" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1507,21 +1508,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380654</v>
+        <v>380708</v>
       </c>
       <c r="R10" t="n">
-        <v>6728875</v>
+        <v>6729212</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120330318</v>
+        <v>120330300</v>
       </c>
       <c r="B11" t="n">
-        <v>56784</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102961</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380696</v>
+        <v>380431</v>
       </c>
       <c r="R11" t="n">
-        <v>6728743</v>
+        <v>6729232</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1696,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330294</v>
+        <v>120330287</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380570</v>
+        <v>380785</v>
       </c>
       <c r="R12" t="n">
-        <v>6729359</v>
+        <v>6729186</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120330301</v>
+        <v>120330321</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1814,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380391</v>
+        <v>380786</v>
       </c>
       <c r="R13" t="n">
-        <v>6729218</v>
+        <v>6728836</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1881,7 +1882,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1900,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330290</v>
+        <v>120330322</v>
       </c>
       <c r="B14" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,21 +1916,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380721</v>
+        <v>380814</v>
       </c>
       <c r="R14" t="n">
-        <v>6729221</v>
+        <v>6728859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120330299</v>
+        <v>120330288</v>
       </c>
       <c r="B15" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,21 +2018,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380431</v>
+        <v>380750</v>
       </c>
       <c r="R15" t="n">
-        <v>6729232</v>
+        <v>6729215</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120330324</v>
+        <v>120330285</v>
       </c>
       <c r="B16" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380873</v>
+        <v>380783</v>
       </c>
       <c r="R16" t="n">
-        <v>6728919</v>
+        <v>6729158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120330302</v>
+        <v>120330320</v>
       </c>
       <c r="B17" t="n">
-        <v>79160</v>
+        <v>74646</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,21 +2222,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380378</v>
+        <v>380766</v>
       </c>
       <c r="R17" t="n">
-        <v>6729224</v>
+        <v>6728820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,7 +2290,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2309,7 +2308,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120330297</v>
+        <v>120330315</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2349,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380445</v>
+        <v>380671</v>
       </c>
       <c r="R18" t="n">
-        <v>6729259</v>
+        <v>6728902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330296</v>
+        <v>120330292</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2529,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2553,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380544</v>
+        <v>380661</v>
       </c>
       <c r="R20" t="n">
-        <v>6729316</v>
+        <v>6729256</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2615,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330316</v>
+        <v>120330308</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2627,25 +2626,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2655,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380649</v>
+        <v>380515</v>
       </c>
       <c r="R21" t="n">
-        <v>6728874</v>
+        <v>6729057</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,10 +2716,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330323</v>
+        <v>120330296</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2733,21 +2732,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2757,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380832</v>
+        <v>380544</v>
       </c>
       <c r="R22" t="n">
-        <v>6728895</v>
+        <v>6729316</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2819,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330311</v>
+        <v>120330306</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2835,21 +2834,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2859,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380640</v>
+        <v>380509</v>
       </c>
       <c r="R23" t="n">
-        <v>6729019</v>
+        <v>6729054</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2921,7 +2920,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120330287</v>
+        <v>120330297</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -2961,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380785</v>
+        <v>380445</v>
       </c>
       <c r="R24" t="n">
-        <v>6729186</v>
+        <v>6729259</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120330286</v>
+        <v>120330318</v>
       </c>
       <c r="B25" t="n">
-        <v>86895</v>
+        <v>56784</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3039,21 +3038,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>510</v>
+        <v>102961</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3063,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380781</v>
+        <v>380696</v>
       </c>
       <c r="R25" t="n">
-        <v>6729159</v>
+        <v>6728743</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3125,7 +3124,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120330312</v>
+        <v>120330311</v>
       </c>
       <c r="B26" t="n">
         <v>78542</v>
@@ -3165,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380707</v>
+        <v>380640</v>
       </c>
       <c r="R26" t="n">
-        <v>6729068</v>
+        <v>6729019</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120330291</v>
+        <v>120330323</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3243,21 +3242,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3267,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380708</v>
+        <v>380832</v>
       </c>
       <c r="R27" t="n">
-        <v>6729212</v>
+        <v>6728895</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,10 +3328,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120330320</v>
+        <v>120330324</v>
       </c>
       <c r="B28" t="n">
-        <v>74646</v>
+        <v>78278</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3345,21 +3344,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>308</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380766</v>
+        <v>380873</v>
       </c>
       <c r="R28" t="n">
-        <v>6728820</v>
+        <v>6728919</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120330300</v>
+        <v>120330295</v>
       </c>
       <c r="B29" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3447,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3471,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380431</v>
+        <v>380564</v>
       </c>
       <c r="R29" t="n">
-        <v>6729232</v>
+        <v>6729347</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3533,10 +3532,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120330315</v>
+        <v>120330302</v>
       </c>
       <c r="B30" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3549,21 +3548,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3573,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380671</v>
+        <v>380378</v>
       </c>
       <c r="R30" t="n">
-        <v>6728902</v>
+        <v>6729224</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3617,6 +3616,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330285</v>
+        <v>120330299</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380783</v>
+        <v>380431</v>
       </c>
       <c r="R31" t="n">
-        <v>6729158</v>
+        <v>6729232</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330303</v>
+        <v>120330310</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3749,25 +3749,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380366</v>
+        <v>380648</v>
       </c>
       <c r="R32" t="n">
-        <v>6729220</v>
+        <v>6729011</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330292</v>
+        <v>120330319</v>
       </c>
       <c r="B33" t="n">
-        <v>78278</v>
+        <v>90545</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3851,25 +3851,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380661</v>
+        <v>380743</v>
       </c>
       <c r="R33" t="n">
-        <v>6729256</v>
+        <v>6728768</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330289</v>
+        <v>120330309</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3953,25 +3953,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380729</v>
+        <v>380597</v>
       </c>
       <c r="R34" t="n">
-        <v>6729223</v>
+        <v>6728960</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330308</v>
+        <v>120330316</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4055,25 +4055,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380515</v>
+        <v>380649</v>
       </c>
       <c r="R35" t="n">
-        <v>6729057</v>
+        <v>6728874</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330313</v>
+        <v>120330286</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>86895</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380704</v>
+        <v>380781</v>
       </c>
       <c r="R36" t="n">
-        <v>6729068</v>
+        <v>6729159</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330306</v>
+        <v>120330312</v>
       </c>
       <c r="B37" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380509</v>
+        <v>380707</v>
       </c>
       <c r="R37" t="n">
-        <v>6729054</v>
+        <v>6729068</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120330309</v>
+        <v>120330290</v>
       </c>
       <c r="B38" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4361,25 +4361,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380597</v>
+        <v>380721</v>
       </c>
       <c r="R38" t="n">
-        <v>6728960</v>
+        <v>6729221</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120330293</v>
+        <v>120330294</v>
       </c>
       <c r="B39" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380661</v>
+        <v>380570</v>
       </c>
       <c r="R39" t="n">
-        <v>6729256</v>
+        <v>6729359</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120330303</v>
+        <v>120330321</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380366</v>
+        <v>380786</v>
       </c>
       <c r="R2" t="n">
-        <v>6729220</v>
+        <v>6728836</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330317</v>
+        <v>120330315</v>
       </c>
       <c r="B3" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380654</v>
+        <v>380671</v>
       </c>
       <c r="R3" t="n">
-        <v>6728875</v>
+        <v>6728902</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330301</v>
+        <v>120330296</v>
       </c>
       <c r="B4" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380391</v>
+        <v>380544</v>
       </c>
       <c r="R4" t="n">
-        <v>6729218</v>
+        <v>6729316</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330289</v>
+        <v>120330285</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1022,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380729</v>
+        <v>380783</v>
       </c>
       <c r="R5" t="n">
-        <v>6729223</v>
+        <v>6729158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330293</v>
+        <v>120330300</v>
       </c>
       <c r="B6" t="n">
         <v>78279</v>
@@ -1124,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380661</v>
+        <v>380431</v>
       </c>
       <c r="R6" t="n">
-        <v>6729256</v>
+        <v>6729232</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330304</v>
+        <v>120330288</v>
       </c>
       <c r="B7" t="n">
-        <v>80499</v>
+        <v>78576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1049</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1226,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380372</v>
+        <v>380750</v>
       </c>
       <c r="R7" t="n">
-        <v>6729180</v>
+        <v>6729215</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1288,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330313</v>
+        <v>120330289</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1328,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380704</v>
+        <v>380729</v>
       </c>
       <c r="R8" t="n">
-        <v>6729068</v>
+        <v>6729223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1390,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330298</v>
+        <v>120330286</v>
       </c>
       <c r="B9" t="n">
-        <v>77474</v>
+        <v>86895</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6487</v>
+        <v>510</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1430,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380418</v>
+        <v>380781</v>
       </c>
       <c r="R9" t="n">
-        <v>6729265</v>
+        <v>6729159</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1492,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120330291</v>
+        <v>120330308</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1532,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380708</v>
+        <v>380515</v>
       </c>
       <c r="R10" t="n">
-        <v>6729212</v>
+        <v>6729057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1594,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120330300</v>
+        <v>120330324</v>
       </c>
       <c r="B11" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1634,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380431</v>
+        <v>380873</v>
       </c>
       <c r="R11" t="n">
-        <v>6729232</v>
+        <v>6728919</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1696,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330287</v>
+        <v>120330291</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1736,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380785</v>
+        <v>380708</v>
       </c>
       <c r="R12" t="n">
-        <v>6729186</v>
+        <v>6729212</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1798,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120330321</v>
+        <v>120330292</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1838,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380786</v>
+        <v>380661</v>
       </c>
       <c r="R13" t="n">
-        <v>6728836</v>
+        <v>6729256</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330322</v>
+        <v>120330317</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1916,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1940,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380814</v>
+        <v>380654</v>
       </c>
       <c r="R14" t="n">
-        <v>6728859</v>
+        <v>6728875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120330288</v>
+        <v>120330316</v>
       </c>
       <c r="B15" t="n">
-        <v>78576</v>
+        <v>90545</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2014,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380750</v>
+        <v>380649</v>
       </c>
       <c r="R15" t="n">
-        <v>6729215</v>
+        <v>6728874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120330285</v>
+        <v>120330305</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2144,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380783</v>
+        <v>380455</v>
       </c>
       <c r="R16" t="n">
-        <v>6729158</v>
+        <v>6729080</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120330320</v>
+        <v>120330303</v>
       </c>
       <c r="B17" t="n">
-        <v>74646</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2222,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380766</v>
+        <v>380366</v>
       </c>
       <c r="R17" t="n">
-        <v>6728820</v>
+        <v>6729220</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120330315</v>
+        <v>120330294</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2348,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380671</v>
+        <v>380570</v>
       </c>
       <c r="R18" t="n">
-        <v>6728902</v>
+        <v>6729359</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2409,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330305</v>
+        <v>120330311</v>
       </c>
       <c r="B19" t="n">
         <v>78542</v>
@@ -2450,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380455</v>
+        <v>380640</v>
       </c>
       <c r="R19" t="n">
-        <v>6729080</v>
+        <v>6729019</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330292</v>
+        <v>120330306</v>
       </c>
       <c r="B20" t="n">
-        <v>78278</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380661</v>
+        <v>380509</v>
       </c>
       <c r="R20" t="n">
-        <v>6729256</v>
+        <v>6729054</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330308</v>
+        <v>120330309</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2626,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2654,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380515</v>
+        <v>380597</v>
       </c>
       <c r="R21" t="n">
-        <v>6729057</v>
+        <v>6728960</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,10 +2715,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330296</v>
+        <v>120330323</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>78576</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,21 +2731,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380544</v>
+        <v>380832</v>
       </c>
       <c r="R22" t="n">
-        <v>6729316</v>
+        <v>6728895</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330306</v>
+        <v>120330318</v>
       </c>
       <c r="B23" t="n">
-        <v>57473</v>
+        <v>56784</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2834,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>102961</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2858,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380509</v>
+        <v>380696</v>
       </c>
       <c r="R23" t="n">
-        <v>6729054</v>
+        <v>6728743</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120330297</v>
+        <v>120330312</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -2960,10 +2959,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380445</v>
+        <v>380707</v>
       </c>
       <c r="R24" t="n">
-        <v>6729259</v>
+        <v>6729068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120330318</v>
+        <v>120330287</v>
       </c>
       <c r="B25" t="n">
-        <v>56784</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102961</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380696</v>
+        <v>380785</v>
       </c>
       <c r="R25" t="n">
-        <v>6728743</v>
+        <v>6729186</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,10 +3123,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120330311</v>
+        <v>120330302</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,21 +3139,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3164,10 +3163,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380640</v>
+        <v>380378</v>
       </c>
       <c r="R26" t="n">
-        <v>6729019</v>
+        <v>6729224</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3208,6 +3207,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3226,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120330323</v>
+        <v>120330295</v>
       </c>
       <c r="B27" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3242,21 +3242,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380832</v>
+        <v>380564</v>
       </c>
       <c r="R27" t="n">
-        <v>6728895</v>
+        <v>6729347</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120330324</v>
+        <v>120330298</v>
       </c>
       <c r="B28" t="n">
-        <v>78278</v>
+        <v>77474</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380873</v>
+        <v>380418</v>
       </c>
       <c r="R28" t="n">
-        <v>6728919</v>
+        <v>6729265</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120330295</v>
+        <v>120330301</v>
       </c>
       <c r="B29" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380564</v>
+        <v>380391</v>
       </c>
       <c r="R29" t="n">
-        <v>6729347</v>
+        <v>6729218</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3514,6 +3514,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3533,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120330302</v>
+        <v>120330290</v>
       </c>
       <c r="B30" t="n">
-        <v>79160</v>
+        <v>78576</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,21 +3549,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3572,10 +3573,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380378</v>
+        <v>380721</v>
       </c>
       <c r="R30" t="n">
-        <v>6729224</v>
+        <v>6729221</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,7 +3617,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330299</v>
+        <v>120330304</v>
       </c>
       <c r="B31" t="n">
-        <v>78278</v>
+        <v>80499</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>1049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380431</v>
+        <v>380372</v>
       </c>
       <c r="R31" t="n">
-        <v>6729232</v>
+        <v>6729180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330310</v>
+        <v>120330297</v>
       </c>
       <c r="B32" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3749,25 +3749,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380648</v>
+        <v>380445</v>
       </c>
       <c r="R32" t="n">
-        <v>6729011</v>
+        <v>6729259</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3839,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330319</v>
+        <v>120330322</v>
       </c>
       <c r="B33" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3851,25 +3851,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380743</v>
+        <v>380814</v>
       </c>
       <c r="R33" t="n">
-        <v>6728768</v>
+        <v>6728859</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330309</v>
+        <v>120330293</v>
       </c>
       <c r="B34" t="n">
-        <v>90545</v>
+        <v>78279</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3953,25 +3953,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380597</v>
+        <v>380661</v>
       </c>
       <c r="R34" t="n">
-        <v>6728960</v>
+        <v>6729256</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,7 +4043,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330316</v>
+        <v>120330319</v>
       </c>
       <c r="B35" t="n">
         <v>90545</v>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380649</v>
+        <v>380743</v>
       </c>
       <c r="R35" t="n">
-        <v>6728874</v>
+        <v>6728768</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330286</v>
+        <v>120330299</v>
       </c>
       <c r="B36" t="n">
-        <v>86895</v>
+        <v>78278</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>510</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380781</v>
+        <v>380431</v>
       </c>
       <c r="R36" t="n">
-        <v>6729159</v>
+        <v>6729232</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,7 +4247,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330312</v>
+        <v>120330313</v>
       </c>
       <c r="B37" t="n">
         <v>78542</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380707</v>
+        <v>380704</v>
       </c>
       <c r="R37" t="n">
         <v>6729068</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120330290</v>
+        <v>120330320</v>
       </c>
       <c r="B38" t="n">
-        <v>78576</v>
+        <v>74646</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>185</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380721</v>
+        <v>380766</v>
       </c>
       <c r="R38" t="n">
-        <v>6729221</v>
+        <v>6728820</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120330294</v>
+        <v>120330310</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4463,25 +4463,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380570</v>
+        <v>380648</v>
       </c>
       <c r="R39" t="n">
-        <v>6729359</v>
+        <v>6729011</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120330321</v>
+        <v>120330315</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380786</v>
+        <v>380671</v>
       </c>
       <c r="R2" t="n">
-        <v>6728836</v>
+        <v>6728902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330315</v>
+        <v>120330296</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380671</v>
+        <v>380544</v>
       </c>
       <c r="R3" t="n">
-        <v>6728902</v>
+        <v>6729316</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330296</v>
+        <v>120330321</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380544</v>
+        <v>380786</v>
       </c>
       <c r="R4" t="n">
-        <v>6729316</v>
+        <v>6728836</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330311</v>
+        <v>120330309</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380640</v>
+        <v>380597</v>
       </c>
       <c r="R19" t="n">
-        <v>6729019</v>
+        <v>6728960</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330306</v>
+        <v>120330311</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380509</v>
+        <v>380640</v>
       </c>
       <c r="R20" t="n">
-        <v>6729054</v>
+        <v>6729019</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330309</v>
+        <v>120330306</v>
       </c>
       <c r="B21" t="n">
-        <v>90545</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2625,25 +2625,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380597</v>
+        <v>380509</v>
       </c>
       <c r="R21" t="n">
-        <v>6728960</v>
+        <v>6729054</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120330315</v>
+        <v>120330316</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380671</v>
+        <v>380649</v>
       </c>
       <c r="R2" t="n">
-        <v>6728902</v>
+        <v>6728874</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330296</v>
+        <v>120330309</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380544</v>
+        <v>380597</v>
       </c>
       <c r="R3" t="n">
-        <v>6729316</v>
+        <v>6728960</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330321</v>
+        <v>120330287</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380786</v>
+        <v>380785</v>
       </c>
       <c r="R4" t="n">
-        <v>6728836</v>
+        <v>6729186</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330285</v>
+        <v>120330321</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380783</v>
+        <v>380786</v>
       </c>
       <c r="R5" t="n">
-        <v>6729158</v>
+        <v>6728836</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330300</v>
+        <v>120330291</v>
       </c>
       <c r="B6" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380431</v>
+        <v>380708</v>
       </c>
       <c r="R6" t="n">
-        <v>6729232</v>
+        <v>6729212</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330288</v>
+        <v>120330300</v>
       </c>
       <c r="B7" t="n">
-        <v>78576</v>
+        <v>78279</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380750</v>
+        <v>380431</v>
       </c>
       <c r="R7" t="n">
-        <v>6729215</v>
+        <v>6729232</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330289</v>
+        <v>120330317</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380729</v>
+        <v>380654</v>
       </c>
       <c r="R8" t="n">
-        <v>6729223</v>
+        <v>6728875</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330286</v>
+        <v>120330306</v>
       </c>
       <c r="B9" t="n">
-        <v>86895</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>510</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380781</v>
+        <v>380509</v>
       </c>
       <c r="R9" t="n">
-        <v>6729159</v>
+        <v>6729054</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120330308</v>
+        <v>120330310</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380515</v>
+        <v>380648</v>
       </c>
       <c r="R10" t="n">
-        <v>6729057</v>
+        <v>6729011</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120330324</v>
+        <v>120330305</v>
       </c>
       <c r="B11" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380873</v>
+        <v>380455</v>
       </c>
       <c r="R11" t="n">
-        <v>6728919</v>
+        <v>6729080</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330291</v>
+        <v>120330312</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380708</v>
+        <v>380707</v>
       </c>
       <c r="R12" t="n">
-        <v>6729212</v>
+        <v>6729068</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120330292</v>
+        <v>120330286</v>
       </c>
       <c r="B13" t="n">
-        <v>78278</v>
+        <v>86895</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380661</v>
+        <v>380781</v>
       </c>
       <c r="R13" t="n">
-        <v>6729256</v>
+        <v>6729159</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330317</v>
+        <v>120330303</v>
       </c>
       <c r="B14" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380654</v>
+        <v>380366</v>
       </c>
       <c r="R14" t="n">
-        <v>6728875</v>
+        <v>6729220</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120330316</v>
+        <v>120330311</v>
       </c>
       <c r="B15" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2013,25 +2013,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380649</v>
+        <v>380640</v>
       </c>
       <c r="R15" t="n">
-        <v>6728874</v>
+        <v>6729019</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120330305</v>
+        <v>120330319</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380455</v>
+        <v>380743</v>
       </c>
       <c r="R16" t="n">
-        <v>6729080</v>
+        <v>6728768</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120330303</v>
+        <v>120330324</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380366</v>
+        <v>380873</v>
       </c>
       <c r="R17" t="n">
-        <v>6729220</v>
+        <v>6728919</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120330294</v>
+        <v>120330295</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2347,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380570</v>
+        <v>380564</v>
       </c>
       <c r="R18" t="n">
-        <v>6729359</v>
+        <v>6729347</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2409,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330309</v>
+        <v>120330290</v>
       </c>
       <c r="B19" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2421,25 +2421,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2449,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380597</v>
+        <v>380721</v>
       </c>
       <c r="R19" t="n">
-        <v>6728960</v>
+        <v>6729221</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330311</v>
+        <v>120330304</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>80499</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2527,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>1049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380640</v>
+        <v>380372</v>
       </c>
       <c r="R20" t="n">
-        <v>6729019</v>
+        <v>6729180</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2613,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330306</v>
+        <v>120330294</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2629,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2653,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380509</v>
+        <v>380570</v>
       </c>
       <c r="R21" t="n">
-        <v>6729054</v>
+        <v>6729359</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2715,7 +2715,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330323</v>
+        <v>120330288</v>
       </c>
       <c r="B22" t="n">
         <v>78576</v>
@@ -2755,10 +2755,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380832</v>
+        <v>380750</v>
       </c>
       <c r="R22" t="n">
-        <v>6728895</v>
+        <v>6729215</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2817,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330318</v>
+        <v>120330323</v>
       </c>
       <c r="B23" t="n">
-        <v>56784</v>
+        <v>78576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2833,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102961</v>
+        <v>185</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2857,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380696</v>
+        <v>380832</v>
       </c>
       <c r="R23" t="n">
-        <v>6728743</v>
+        <v>6728895</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2919,7 +2919,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120330312</v>
+        <v>120330313</v>
       </c>
       <c r="B24" t="n">
         <v>78542</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>380707</v>
+        <v>380704</v>
       </c>
       <c r="R24" t="n">
         <v>6729068</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120330287</v>
+        <v>120330302</v>
       </c>
       <c r="B25" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3037,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380785</v>
+        <v>380378</v>
       </c>
       <c r="R25" t="n">
-        <v>6729186</v>
+        <v>6729224</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,6 +3105,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3123,10 +3124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120330302</v>
+        <v>120330296</v>
       </c>
       <c r="B26" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3139,21 +3140,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3163,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>380378</v>
+        <v>380544</v>
       </c>
       <c r="R26" t="n">
-        <v>6729224</v>
+        <v>6729316</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3207,7 +3208,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3226,7 +3226,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120330295</v>
+        <v>120330297</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3266,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380564</v>
+        <v>380445</v>
       </c>
       <c r="R27" t="n">
-        <v>6729347</v>
+        <v>6729259</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3328,10 +3328,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120330298</v>
+        <v>120330318</v>
       </c>
       <c r="B28" t="n">
-        <v>77474</v>
+        <v>56784</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,21 +3344,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6487</v>
+        <v>102961</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3368,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380418</v>
+        <v>380696</v>
       </c>
       <c r="R28" t="n">
-        <v>6729265</v>
+        <v>6728743</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120330301</v>
+        <v>120330320</v>
       </c>
       <c r="B29" t="n">
-        <v>78278</v>
+        <v>74646</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,21 +3446,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380391</v>
+        <v>380766</v>
       </c>
       <c r="R29" t="n">
-        <v>6729218</v>
+        <v>6728820</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3514,7 +3514,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3533,10 +3532,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120330290</v>
+        <v>120330292</v>
       </c>
       <c r="B30" t="n">
-        <v>78576</v>
+        <v>78278</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3549,21 +3548,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3573,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380721</v>
+        <v>380661</v>
       </c>
       <c r="R30" t="n">
-        <v>6729221</v>
+        <v>6729256</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330304</v>
+        <v>120330308</v>
       </c>
       <c r="B31" t="n">
-        <v>80499</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3651,21 +3650,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3674,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380372</v>
+        <v>380515</v>
       </c>
       <c r="R31" t="n">
-        <v>6729180</v>
+        <v>6729057</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3737,10 +3736,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330297</v>
+        <v>120330298</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>77474</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3753,21 +3752,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3777,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380445</v>
+        <v>380418</v>
       </c>
       <c r="R32" t="n">
-        <v>6729259</v>
+        <v>6729265</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3941,10 +3940,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330293</v>
+        <v>120330301</v>
       </c>
       <c r="B34" t="n">
-        <v>78279</v>
+        <v>78278</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3957,21 +3956,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3980,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380661</v>
+        <v>380391</v>
       </c>
       <c r="R34" t="n">
-        <v>6729256</v>
+        <v>6729218</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4025,6 +4024,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330319</v>
+        <v>120330285</v>
       </c>
       <c r="B35" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4055,25 +4055,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380743</v>
+        <v>380783</v>
       </c>
       <c r="R35" t="n">
-        <v>6728768</v>
+        <v>6729158</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330299</v>
+        <v>120330289</v>
       </c>
       <c r="B36" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380431</v>
+        <v>380729</v>
       </c>
       <c r="R36" t="n">
-        <v>6729232</v>
+        <v>6729223</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330313</v>
+        <v>120330293</v>
       </c>
       <c r="B37" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380704</v>
+        <v>380661</v>
       </c>
       <c r="R37" t="n">
-        <v>6729068</v>
+        <v>6729256</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120330320</v>
+        <v>120330315</v>
       </c>
       <c r="B38" t="n">
-        <v>74646</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380766</v>
+        <v>380671</v>
       </c>
       <c r="R38" t="n">
-        <v>6728820</v>
+        <v>6728902</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120330310</v>
+        <v>120330299</v>
       </c>
       <c r="B39" t="n">
-        <v>90545</v>
+        <v>78278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4463,25 +4463,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380648</v>
+        <v>380431</v>
       </c>
       <c r="R39" t="n">
-        <v>6729011</v>
+        <v>6729232</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120330316</v>
+        <v>120330290</v>
       </c>
       <c r="B2" t="n">
-        <v>90545</v>
+        <v>78576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>380649</v>
+        <v>380721</v>
       </c>
       <c r="R2" t="n">
-        <v>6728874</v>
+        <v>6729221</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120330309</v>
+        <v>120330322</v>
       </c>
       <c r="B3" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>380597</v>
+        <v>380814</v>
       </c>
       <c r="R3" t="n">
-        <v>6728960</v>
+        <v>6728859</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120330287</v>
+        <v>120330319</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>380785</v>
+        <v>380743</v>
       </c>
       <c r="R4" t="n">
-        <v>6729186</v>
+        <v>6728768</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330321</v>
+        <v>120330305</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380786</v>
+        <v>380455</v>
       </c>
       <c r="R5" t="n">
-        <v>6728836</v>
+        <v>6729080</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330291</v>
+        <v>120330308</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380708</v>
+        <v>380515</v>
       </c>
       <c r="R6" t="n">
-        <v>6729212</v>
+        <v>6729057</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330300</v>
+        <v>120330315</v>
       </c>
       <c r="B7" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380431</v>
+        <v>380671</v>
       </c>
       <c r="R7" t="n">
-        <v>6729232</v>
+        <v>6728902</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330317</v>
+        <v>120330294</v>
       </c>
       <c r="B8" t="n">
-        <v>82321</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380654</v>
+        <v>380570</v>
       </c>
       <c r="R8" t="n">
-        <v>6728875</v>
+        <v>6729359</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330306</v>
+        <v>120330293</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>78279</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380509</v>
+        <v>380661</v>
       </c>
       <c r="R9" t="n">
-        <v>6729054</v>
+        <v>6729256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120330310</v>
+        <v>120330291</v>
       </c>
       <c r="B10" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>380648</v>
+        <v>380708</v>
       </c>
       <c r="R10" t="n">
-        <v>6729011</v>
+        <v>6729212</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120330305</v>
+        <v>120330300</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>380455</v>
+        <v>380431</v>
       </c>
       <c r="R11" t="n">
-        <v>6729080</v>
+        <v>6729232</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120330312</v>
+        <v>120330289</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>380707</v>
+        <v>380729</v>
       </c>
       <c r="R12" t="n">
-        <v>6729068</v>
+        <v>6729223</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120330286</v>
+        <v>120330320</v>
       </c>
       <c r="B13" t="n">
-        <v>86895</v>
+        <v>74646</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1813,21 +1813,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>380781</v>
+        <v>380766</v>
       </c>
       <c r="R13" t="n">
-        <v>6729159</v>
+        <v>6728820</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120330303</v>
+        <v>120330317</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>380366</v>
+        <v>380654</v>
       </c>
       <c r="R14" t="n">
-        <v>6729220</v>
+        <v>6728875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120330311</v>
+        <v>120330302</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>380640</v>
+        <v>380378</v>
       </c>
       <c r="R15" t="n">
-        <v>6729019</v>
+        <v>6729224</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2085,6 +2085,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2103,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120330319</v>
+        <v>120330287</v>
       </c>
       <c r="B16" t="n">
-        <v>90545</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2116,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>380743</v>
+        <v>380785</v>
       </c>
       <c r="R16" t="n">
-        <v>6728768</v>
+        <v>6729186</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120330324</v>
+        <v>120330311</v>
       </c>
       <c r="B17" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2222,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>380873</v>
+        <v>380640</v>
       </c>
       <c r="R17" t="n">
-        <v>6728919</v>
+        <v>6729019</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2307,7 +2308,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120330295</v>
+        <v>120330321</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2347,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>380564</v>
+        <v>380786</v>
       </c>
       <c r="R18" t="n">
-        <v>6729347</v>
+        <v>6728836</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2409,10 +2410,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120330290</v>
+        <v>120330303</v>
       </c>
       <c r="B19" t="n">
-        <v>78576</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2425,21 +2426,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2449,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>380721</v>
+        <v>380366</v>
       </c>
       <c r="R19" t="n">
-        <v>6729221</v>
+        <v>6729220</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120330304</v>
+        <v>120330286</v>
       </c>
       <c r="B20" t="n">
-        <v>80499</v>
+        <v>86895</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2527,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1049</v>
+        <v>510</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2551,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>380372</v>
+        <v>380781</v>
       </c>
       <c r="R20" t="n">
-        <v>6729180</v>
+        <v>6729159</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2613,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120330294</v>
+        <v>120330301</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2629,21 +2630,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2653,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>380570</v>
+        <v>380391</v>
       </c>
       <c r="R21" t="n">
-        <v>6729359</v>
+        <v>6729218</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2697,6 +2698,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2715,10 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120330288</v>
+        <v>120330298</v>
       </c>
       <c r="B22" t="n">
-        <v>78576</v>
+        <v>77474</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2731,21 +2733,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2755,10 +2757,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>380750</v>
+        <v>380418</v>
       </c>
       <c r="R22" t="n">
-        <v>6729215</v>
+        <v>6729265</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,10 +2819,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120330323</v>
+        <v>120330324</v>
       </c>
       <c r="B23" t="n">
-        <v>78576</v>
+        <v>78278</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2833,21 +2835,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2857,10 +2859,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>380832</v>
+        <v>380873</v>
       </c>
       <c r="R23" t="n">
-        <v>6728895</v>
+        <v>6728919</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3021,10 +3023,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120330302</v>
+        <v>120330297</v>
       </c>
       <c r="B25" t="n">
-        <v>79160</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3037,21 +3039,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3061,10 +3063,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>380378</v>
+        <v>380445</v>
       </c>
       <c r="R25" t="n">
-        <v>6729224</v>
+        <v>6729259</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,7 +3107,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3226,7 +3227,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120330297</v>
+        <v>120330295</v>
       </c>
       <c r="B27" t="n">
         <v>78542</v>
@@ -3266,10 +3267,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>380445</v>
+        <v>380564</v>
       </c>
       <c r="R27" t="n">
-        <v>6729259</v>
+        <v>6729347</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3328,10 +3329,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120330318</v>
+        <v>120330304</v>
       </c>
       <c r="B28" t="n">
-        <v>56784</v>
+        <v>80499</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3344,21 +3345,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102961</v>
+        <v>1049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3368,10 +3369,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>380696</v>
+        <v>380372</v>
       </c>
       <c r="R28" t="n">
-        <v>6728743</v>
+        <v>6729180</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,10 +3431,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120330320</v>
+        <v>120330316</v>
       </c>
       <c r="B29" t="n">
-        <v>74646</v>
+        <v>90545</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3442,25 +3443,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>308</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3471,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>380766</v>
+        <v>380649</v>
       </c>
       <c r="R29" t="n">
-        <v>6728820</v>
+        <v>6728874</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3634,7 +3635,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330308</v>
+        <v>120330312</v>
       </c>
       <c r="B31" t="n">
         <v>78542</v>
@@ -3674,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380515</v>
+        <v>380707</v>
       </c>
       <c r="R31" t="n">
-        <v>6729057</v>
+        <v>6729068</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3736,10 +3737,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120330298</v>
+        <v>120330310</v>
       </c>
       <c r="B32" t="n">
-        <v>77474</v>
+        <v>90545</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3748,25 +3749,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3777,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>380418</v>
+        <v>380648</v>
       </c>
       <c r="R32" t="n">
-        <v>6729265</v>
+        <v>6729011</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3838,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120330322</v>
+        <v>120330299</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3854,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3878,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>380814</v>
+        <v>380431</v>
       </c>
       <c r="R33" t="n">
-        <v>6728859</v>
+        <v>6729232</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3940,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120330301</v>
+        <v>120330323</v>
       </c>
       <c r="B34" t="n">
-        <v>78278</v>
+        <v>78576</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3956,21 +3957,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3980,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>380391</v>
+        <v>380832</v>
       </c>
       <c r="R34" t="n">
-        <v>6729218</v>
+        <v>6728895</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,7 +4025,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4043,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120330285</v>
+        <v>120330309</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>90545</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4055,25 +4055,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>380783</v>
+        <v>380597</v>
       </c>
       <c r="R35" t="n">
-        <v>6729158</v>
+        <v>6728960</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4145,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120330289</v>
+        <v>120330306</v>
       </c>
       <c r="B36" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4161,21 +4161,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>380729</v>
+        <v>380509</v>
       </c>
       <c r="R36" t="n">
-        <v>6729223</v>
+        <v>6729054</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4247,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120330293</v>
+        <v>120330288</v>
       </c>
       <c r="B37" t="n">
-        <v>78279</v>
+        <v>78576</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>380661</v>
+        <v>380750</v>
       </c>
       <c r="R37" t="n">
-        <v>6729256</v>
+        <v>6729215</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120330315</v>
+        <v>120330285</v>
       </c>
       <c r="B38" t="n">
         <v>78542</v>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>380671</v>
+        <v>380783</v>
       </c>
       <c r="R38" t="n">
-        <v>6728902</v>
+        <v>6729158</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120330299</v>
+        <v>120330318</v>
       </c>
       <c r="B39" t="n">
-        <v>78278</v>
+        <v>56784</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>102961</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>380431</v>
+        <v>380696</v>
       </c>
       <c r="R39" t="n">
-        <v>6729232</v>
+        <v>6728743</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>

--- a/artfynd/A 20895-2021 artfynd.xlsx
+++ b/artfynd/A 20895-2021 artfynd.xlsx
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120330305</v>
+        <v>120330293</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>380455</v>
+        <v>380661</v>
       </c>
       <c r="R5" t="n">
-        <v>6729080</v>
+        <v>6729256</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120330308</v>
+        <v>120330305</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>380515</v>
+        <v>380455</v>
       </c>
       <c r="R6" t="n">
-        <v>6729057</v>
+        <v>6729080</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120330315</v>
+        <v>120330308</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>380671</v>
+        <v>380515</v>
       </c>
       <c r="R7" t="n">
-        <v>6728902</v>
+        <v>6729057</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120330294</v>
+        <v>120330315</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>380570</v>
+        <v>380671</v>
       </c>
       <c r="R8" t="n">
-        <v>6729359</v>
+        <v>6728902</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120330293</v>
+        <v>120330294</v>
       </c>
       <c r="B9" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1405,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>380661</v>
+        <v>380570</v>
       </c>
       <c r="R9" t="n">
-        <v>6729256</v>
+        <v>6729359</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -3533,10 +3533,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120330292</v>
+        <v>120330312</v>
       </c>
       <c r="B30" t="n">
-        <v>78278</v>
+        <v>78542</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3549,21 +3549,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3573,10 +3573,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>380661</v>
+        <v>380707</v>
       </c>
       <c r="R30" t="n">
-        <v>6729256</v>
+        <v>6729068</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3635,10 +3635,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120330312</v>
+        <v>120330292</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>78278</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3651,21 +3651,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>380707</v>
+        <v>380661</v>
       </c>
       <c r="R31" t="n">
-        <v>6729068</v>
+        <v>6729256</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
